--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-practitionerrole.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-practitionerrole.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -651,7 +651,7 @@
     <t>代理店に関連する特定の専門分野。 / Specific specialty associated with the agency.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -688,7 +688,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(HealthcareService)
+    <t xml:space="preserve">Reference(HealthcareService|4.0.1)
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>PractitionerRole.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
